--- a/data/config/aplicacoes_fundos.xlsx
+++ b/data/config/aplicacoes_fundos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\Aplicativos e Programação\Tesouraria\App Tesouraria Botuverá\Código\data\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3EC2EB-6233-4C8F-8217-298F1EF6B1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCA7454-14D8-486F-A6A9-172E59AE8ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-16425" windowWidth="29040" windowHeight="15840" xr2:uid="{7416F21D-5932-4029-913F-23D06D3BD085}"/>
+    <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{7416F21D-5932-4029-913F-23D06D3BD085}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="16">
   <si>
     <t xml:space="preserve">Conta </t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>Bradesco Zupo FIF CIC RF CP LP RL</t>
+  </si>
+  <si>
+    <t>XP BANCOS FIRF REFERENCIADA DI CP RL</t>
+  </si>
+  <si>
+    <t>XP BANCOS FIC DE FIRF REFERENCIADO DI CP - RL</t>
   </si>
 </sst>
 </file>
@@ -432,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA1C7B1-216A-4C6A-B3D2-C0F16635EE8F}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
@@ -883,6 +889,57 @@
         <v>1500783.35</v>
       </c>
     </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>7983962</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46279</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>7983962</v>
+      </c>
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="1">
+        <v>46279</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>7983962</v>
+      </c>
+      <c r="B29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="1">
+        <v>46282</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="2">
+        <v>808000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data/config/aplicacoes_fundos.xlsx
+++ b/data/config/aplicacoes_fundos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Computador\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABCA7454-14D8-486F-A6A9-172E59AE8ABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D1A8209-C801-4D64-B184-ED3FED398374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-225" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{7416F21D-5932-4029-913F-23D06D3BD085}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="16">
   <si>
     <t xml:space="preserve">Conta </t>
   </si>
@@ -438,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAA1C7B1-216A-4C6A-B3D2-C0F16635EE8F}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
@@ -940,6 +940,23 @@
         <v>808000</v>
       </c>
     </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>5166121</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="1">
+        <v>46282</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2003091</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
